--- a/device-management/templates/到访导入_成功演示.xlsx
+++ b/device-management/templates/到访导入_成功演示.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访明细" sheetId="1" r:id="Re28d40ae2f4e4587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R7f6cb267a9c34002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访明细" sheetId="1" r:id="R729d2df60bc04754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R57c29cfc362943ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -161,7 +161,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="61">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -332,6 +332,9 @@
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -538,15 +541,15 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
@@ -572,30 +575,32 @@
         <x:v>所属门店</x:v>
       </x:c>
       <x:c r="C1" s="54" t="str">
+        <x:v>顾问 ID</x:v>
+      </x:c>
+      <x:c r="D1" s="54" t="str">
         <x:v>顾问姓名</x:v>
       </x:c>
-      <x:c r="D1" s="54" t="str">
+      <x:c r="E1" s="54" t="str">
         <x:v>客户名称</x:v>
       </x:c>
-      <x:c r="E1" s="54" t="str">
+      <x:c r="F1" s="54" t="str">
         <x:v>客户号码</x:v>
       </x:c>
-      <x:c r="F1" s="54" t="str">
+      <x:c r="G1" s="54" t="str">
         <x:v>业务场景</x:v>
       </x:c>
-      <x:c r="G1" s="54" t="str">
+      <x:c r="H1" s="54" t="str">
         <x:v>意向车系</x:v>
       </x:c>
-      <x:c r="H1" s="54" t="str">
+      <x:c r="I1" s="54" t="str">
         <x:v>到访日期</x:v>
       </x:c>
-      <x:c r="I1" s="54" t="str">
+      <x:c r="J1" s="54" t="str">
         <x:v>开始时间</x:v>
       </x:c>
-      <x:c r="J1" s="54" t="str">
+      <x:c r="K1" s="54" t="str">
         <x:v>结束时间</x:v>
       </x:c>
-      <x:c r="K1"/>
       <x:c r="L1"/>
       <x:c r="M1"/>
       <x:c r="N1"/>
@@ -620,30 +625,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
+      <x:c r="E2" s="14" t="str">
         <x:v>王先生</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="str">
+      <x:c r="F2" s="14" t="str">
         <x:v>138****0628</x:v>
       </x:c>
-      <x:c r="F2" s="14" t="str">
+      <x:c r="G2" s="14" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="str">
+      <x:c r="H2" s="14" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H2" s="17" t="d">
+      <x:c r="I2" s="17" t="d">
         <x:v>2026-10-13T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I2" s="20" t="n">
+      <x:c r="J2" s="20" t="n">
         <x:v>0.5444444444444444</x:v>
       </x:c>
-      <x:c r="J2" s="20" t="n">
+      <x:c r="K2" s="20" t="n">
         <x:v>0.5611111111111111</x:v>
       </x:c>
-      <x:c r="K2"/>
       <x:c r="L2"/>
       <x:c r="M2"/>
       <x:c r="N2"/>
@@ -668,30 +675,32 @@
         <x:v>杭州奥体</x:v>
       </x:c>
       <x:c r="C3" s="15" t="str">
+        <x:v>DEMO-AION-ZJA0400-01</x:v>
+      </x:c>
+      <x:c r="D3" s="15" t="str">
         <x:v>黄宇辰</x:v>
       </x:c>
-      <x:c r="D3" s="15" t="str">
+      <x:c r="E3" s="15" t="str">
         <x:v>郑女士</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="F3" s="15" t="str">
         <x:v>137****3091</x:v>
       </x:c>
-      <x:c r="F3" s="15" t="str">
+      <x:c r="G3" s="15" t="str">
         <x:v>试乘试驾</x:v>
       </x:c>
-      <x:c r="G3" s="15" t="str">
+      <x:c r="H3" s="15" t="str">
         <x:v>埃安S MAX</x:v>
       </x:c>
-      <x:c r="H3" s="18" t="d">
+      <x:c r="I3" s="18" t="d">
         <x:v>2026-10-12T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I3" s="21" t="n">
+      <x:c r="J3" s="21" t="n">
         <x:v>0.6377314814814815</x:v>
       </x:c>
-      <x:c r="J3" s="21" t="n">
+      <x:c r="K3" s="21" t="n">
         <x:v>0.6616435185185185</x:v>
       </x:c>
-      <x:c r="K3"/>
       <x:c r="L3"/>
       <x:c r="M3"/>
       <x:c r="N3"/>
@@ -716,30 +725,32 @@
         <x:v>苏州苏虹路</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
+        <x:v>DEMO-AION-JSE0600-01</x:v>
+      </x:c>
+      <x:c r="D4" s="15" t="str">
         <x:v>孙诗涵</x:v>
       </x:c>
-      <x:c r="D4" s="15" t="str">
+      <x:c r="E4" s="15" t="str">
         <x:v>吴女士</x:v>
       </x:c>
-      <x:c r="E4" s="15" t="str">
+      <x:c r="F4" s="15" t="str">
         <x:v>136****5826</x:v>
       </x:c>
-      <x:c r="F4" s="15" t="str">
+      <x:c r="G4" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G4" s="15" t="str">
+      <x:c r="H4" s="15" t="str">
         <x:v>昊铂GT</x:v>
       </x:c>
-      <x:c r="H4" s="18" t="d">
+      <x:c r="I4" s="18" t="d">
         <x:v>2026-10-11T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I4" s="21" t="n">
+      <x:c r="J4" s="21" t="n">
         <x:v>0.6084259259259259</x:v>
       </x:c>
-      <x:c r="J4" s="21" t="n">
+      <x:c r="K4" s="21" t="n">
         <x:v>0.6296412037037037</x:v>
       </x:c>
-      <x:c r="K4"/>
       <x:c r="L4"/>
       <x:c r="M4"/>
       <x:c r="N4"/>
@@ -764,30 +775,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D5" s="15" t="str">
+      <x:c r="E5" s="15" t="str">
         <x:v>赵女士</x:v>
       </x:c>
-      <x:c r="E5" s="15" t="str">
+      <x:c r="F5" s="15" t="str">
         <x:v>159****8312</x:v>
       </x:c>
-      <x:c r="F5" s="15" t="str">
+      <x:c r="G5" s="15" t="str">
         <x:v>试乘试驾</x:v>
       </x:c>
-      <x:c r="G5" s="15" t="str">
+      <x:c r="H5" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H5" s="18" t="d">
+      <x:c r="I5" s="18" t="d">
         <x:v>2026-10-10T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I5" s="21" t="n">
+      <x:c r="J5" s="21" t="n">
         <x:v>0.5574652777777778</x:v>
       </x:c>
-      <x:c r="J5" s="21" t="n">
+      <x:c r="K5" s="21" t="n">
         <x:v>0.5806481481481481</x:v>
       </x:c>
-      <x:c r="K5"/>
       <x:c r="L5"/>
       <x:c r="M5"/>
       <x:c r="N5"/>
@@ -812,30 +825,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D6" s="15" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D6" s="15" t="str">
+      <x:c r="E6" s="15" t="str">
         <x:v>郑先生</x:v>
       </x:c>
-      <x:c r="E6" s="15" t="str">
+      <x:c r="F6" s="15" t="str">
         <x:v>136****4195</x:v>
       </x:c>
-      <x:c r="F6" s="15" t="str">
+      <x:c r="G6" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G6" s="15" t="str">
+      <x:c r="H6" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H6" s="18" t="d">
+      <x:c r="I6" s="18" t="d">
         <x:v>2026-10-09T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I6" s="21" t="n">
+      <x:c r="J6" s="21" t="n">
         <x:v>0.5891203703703703</x:v>
       </x:c>
-      <x:c r="J6" s="21" t="n">
+      <x:c r="K6" s="21" t="n">
         <x:v>0.6119444444444444</x:v>
       </x:c>
-      <x:c r="K6"/>
       <x:c r="L6"/>
       <x:c r="M6"/>
       <x:c r="N6"/>
@@ -860,30 +875,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D7" s="15" t="str">
+      <x:c r="E7" s="15" t="str">
         <x:v>吴先生</x:v>
       </x:c>
-      <x:c r="E7" s="15" t="str">
+      <x:c r="F7" s="15" t="str">
         <x:v>137****5220</x:v>
       </x:c>
-      <x:c r="F7" s="15" t="str">
+      <x:c r="G7" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G7" s="15" t="str">
+      <x:c r="H7" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H7" s="18" t="d">
+      <x:c r="I7" s="18" t="d">
         <x:v>2026-10-08T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I7" s="21" t="n">
+      <x:c r="J7" s="21" t="n">
         <x:v>0.629375</x:v>
       </x:c>
-      <x:c r="J7" s="21" t="n">
+      <x:c r="K7" s="21" t="n">
         <x:v>0.654525462962963</x:v>
       </x:c>
-      <x:c r="K7"/>
       <x:c r="L7"/>
       <x:c r="M7"/>
       <x:c r="N7"/>
@@ -908,30 +925,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="str">
+      <x:c r="E8" s="15" t="str">
         <x:v>孙女士</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="str">
+      <x:c r="F8" s="15" t="str">
         <x:v>158****2754</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="str">
+      <x:c r="G8" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="str">
+      <x:c r="H8" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H8" s="18" t="d">
+      <x:c r="I8" s="18" t="d">
         <x:v>2026-10-07T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I8" s="21" t="n">
+      <x:c r="J8" s="21" t="n">
         <x:v>0.6750462962962963</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="K8" s="21" t="n">
         <x:v>0.6940740740740741</x:v>
       </x:c>
-      <x:c r="K8"/>
       <x:c r="L8"/>
       <x:c r="M8"/>
       <x:c r="N8"/>
@@ -956,30 +975,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="str">
+      <x:c r="E9" s="15" t="str">
         <x:v>林先生</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str">
+      <x:c r="F9" s="15" t="str">
         <x:v>133****6187</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="str">
+      <x:c r="G9" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="str">
+      <x:c r="H9" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H9" s="18" t="d">
+      <x:c r="I9" s="18" t="d">
         <x:v>2026-10-13T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I9" s="21" t="n">
+      <x:c r="J9" s="21" t="n">
         <x:v>0.7119907407407408</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="K9" s="21" t="n">
         <x:v>0.7268981481481481</x:v>
       </x:c>
-      <x:c r="K9"/>
       <x:c r="L9"/>
       <x:c r="M9"/>
       <x:c r="N9"/>
@@ -1004,30 +1025,32 @@
         <x:v>杭州奥体</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
+        <x:v>DEMO-AION-ZJA0400-01</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
         <x:v>黄宇辰</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="str">
+      <x:c r="E10" s="15" t="str">
         <x:v>刘先生</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str">
+      <x:c r="F10" s="15" t="str">
         <x:v>186****1045</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="str">
+      <x:c r="G10" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="str">
+      <x:c r="H10" s="15" t="str">
         <x:v>埃安S MAX</x:v>
       </x:c>
-      <x:c r="H10" s="18" t="d">
+      <x:c r="I10" s="18" t="d">
         <x:v>2026-10-12T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I10" s="21" t="n">
+      <x:c r="J10" s="21" t="n">
         <x:v>0.7719328703703704</x:v>
       </x:c>
-      <x:c r="J10" s="21" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>0.7721643518518518</x:v>
       </x:c>
-      <x:c r="K10"/>
       <x:c r="L10"/>
       <x:c r="M10"/>
       <x:c r="N10"/>
@@ -1052,30 +1075,32 @@
         <x:v>杭州奥体</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
+        <x:v>DEMO-AION-ZJA0400-01</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
         <x:v>黄宇辰</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="E11" s="15" t="str">
         <x:v>钱女士</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="F11" s="15" t="str">
         <x:v>189****4036</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str">
+      <x:c r="G11" s="15" t="str">
         <x:v>试乘试驾</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="str">
+      <x:c r="H11" s="15" t="str">
         <x:v>埃安S MAX</x:v>
       </x:c>
-      <x:c r="H11" s="18" t="d">
+      <x:c r="I11" s="18" t="d">
         <x:v>2026-10-11T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I11" s="21" t="n">
+      <x:c r="J11" s="21" t="n">
         <x:v>0.7375925925925926</x:v>
       </x:c>
-      <x:c r="J11" s="21" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>0.7537037037037037</x:v>
       </x:c>
-      <x:c r="K11"/>
       <x:c r="L11"/>
       <x:c r="M11"/>
       <x:c r="N11"/>
@@ -1100,30 +1125,32 @@
         <x:v>苏州苏虹路</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
+        <x:v>DEMO-AION-JSE0600-01</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
         <x:v>孙诗涵</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="E12" s="15" t="str">
         <x:v>沈女士</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="F12" s="15" t="str">
         <x:v>139****7272</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str">
+      <x:c r="G12" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="str">
+      <x:c r="H12" s="15" t="str">
         <x:v>昊铂GT</x:v>
       </x:c>
-      <x:c r="H12" s="18" t="d">
+      <x:c r="I12" s="18" t="d">
         <x:v>2026-10-10T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I12" s="21" t="n">
+      <x:c r="J12" s="21" t="n">
         <x:v>0.6987847222222222</x:v>
       </x:c>
-      <x:c r="J12" s="21" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>0.7108796296296296</x:v>
       </x:c>
-      <x:c r="K12"/>
       <x:c r="L12"/>
       <x:c r="M12"/>
       <x:c r="N12"/>
@@ -1148,30 +1175,32 @@
         <x:v>苏州苏虹路</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
+        <x:v>DEMO-AION-JSE0600-01</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="str">
         <x:v>孙诗涵</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="E13" s="15" t="str">
         <x:v>周女士</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="F13" s="15" t="str">
         <x:v>135****2776</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str">
+      <x:c r="G13" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="str">
+      <x:c r="H13" s="15" t="str">
         <x:v>昊铂GT</x:v>
       </x:c>
-      <x:c r="H13" s="18" t="d">
+      <x:c r="I13" s="18" t="d">
         <x:v>2026-10-09T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I13" s="21" t="n">
+      <x:c r="J13" s="21" t="n">
         <x:v>0.6831134259259259</x:v>
       </x:c>
-      <x:c r="J13" s="21" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>0.713912037037037</x:v>
       </x:c>
-      <x:c r="K13"/>
       <x:c r="L13"/>
       <x:c r="M13"/>
       <x:c r="N13"/>
@@ -1196,30 +1225,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="E14" s="15" t="str">
         <x:v>王先生</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="F14" s="15" t="str">
         <x:v>138****0628</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str">
+      <x:c r="G14" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="str">
+      <x:c r="H14" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H14" s="18" t="d">
+      <x:c r="I14" s="18" t="d">
         <x:v>2026-10-08T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I14" s="21" t="n">
+      <x:c r="J14" s="21" t="n">
         <x:v>0.5444444444444444</x:v>
       </x:c>
-      <x:c r="J14" s="21" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>0.5611111111111111</x:v>
       </x:c>
-      <x:c r="K14"/>
       <x:c r="L14"/>
       <x:c r="M14"/>
       <x:c r="N14"/>
@@ -1244,30 +1275,32 @@
         <x:v>杭州奥体</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
+        <x:v>DEMO-AION-ZJA0400-01</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
         <x:v>黄宇辰</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="E15" s="15" t="str">
         <x:v>郑女士</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="F15" s="15" t="str">
         <x:v>137****3091</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str">
+      <x:c r="G15" s="15" t="str">
         <x:v>试乘试驾</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="str">
+      <x:c r="H15" s="15" t="str">
         <x:v>埃安S MAX</x:v>
       </x:c>
-      <x:c r="H15" s="18" t="d">
+      <x:c r="I15" s="18" t="d">
         <x:v>2026-10-07T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I15" s="21" t="n">
+      <x:c r="J15" s="21" t="n">
         <x:v>0.6377314814814815</x:v>
       </x:c>
-      <x:c r="J15" s="21" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>0.6616435185185185</x:v>
       </x:c>
-      <x:c r="K15"/>
       <x:c r="L15"/>
       <x:c r="M15"/>
       <x:c r="N15"/>
@@ -1292,30 +1325,32 @@
         <x:v>苏州苏虹路</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
+        <x:v>DEMO-AION-JSE0600-01</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
         <x:v>孙诗涵</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="E16" s="15" t="str">
         <x:v>吴女士</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="F16" s="15" t="str">
         <x:v>136****5826</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str">
+      <x:c r="G16" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="str">
+      <x:c r="H16" s="15" t="str">
         <x:v>昊铂GT</x:v>
       </x:c>
-      <x:c r="H16" s="18" t="d">
+      <x:c r="I16" s="18" t="d">
         <x:v>2026-10-13T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I16" s="21" t="n">
+      <x:c r="J16" s="21" t="n">
         <x:v>0.6084259259259259</x:v>
       </x:c>
-      <x:c r="J16" s="21" t="n">
+      <x:c r="K16" s="21" t="n">
         <x:v>0.6296412037037037</x:v>
       </x:c>
-      <x:c r="K16"/>
       <x:c r="L16"/>
       <x:c r="M16"/>
       <x:c r="N16"/>
@@ -1340,30 +1375,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="E17" s="15" t="str">
         <x:v>赵女士</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="F17" s="15" t="str">
         <x:v>159****8312</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str">
+      <x:c r="G17" s="15" t="str">
         <x:v>试乘试驾</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="str">
+      <x:c r="H17" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H17" s="18" t="d">
+      <x:c r="I17" s="18" t="d">
         <x:v>2026-10-12T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I17" s="21" t="n">
+      <x:c r="J17" s="21" t="n">
         <x:v>0.5574652777777778</x:v>
       </x:c>
-      <x:c r="J17" s="21" t="n">
+      <x:c r="K17" s="21" t="n">
         <x:v>0.5806481481481481</x:v>
       </x:c>
-      <x:c r="K17"/>
       <x:c r="L17"/>
       <x:c r="M17"/>
       <x:c r="N17"/>
@@ -1388,30 +1425,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="E18" s="15" t="str">
         <x:v>郑先生</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="F18" s="15" t="str">
         <x:v>136****4195</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str">
+      <x:c r="G18" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="str">
+      <x:c r="H18" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H18" s="18" t="d">
+      <x:c r="I18" s="18" t="d">
         <x:v>2026-10-11T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I18" s="21" t="n">
+      <x:c r="J18" s="21" t="n">
         <x:v>0.5891203703703703</x:v>
       </x:c>
-      <x:c r="J18" s="21" t="n">
+      <x:c r="K18" s="21" t="n">
         <x:v>0.6119444444444444</x:v>
       </x:c>
-      <x:c r="K18"/>
       <x:c r="L18"/>
       <x:c r="M18"/>
       <x:c r="N18"/>
@@ -1436,30 +1475,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="E19" s="15" t="str">
         <x:v>吴先生</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="F19" s="15" t="str">
         <x:v>137****5220</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str">
+      <x:c r="G19" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="str">
+      <x:c r="H19" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H19" s="18" t="d">
+      <x:c r="I19" s="18" t="d">
         <x:v>2026-10-10T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I19" s="21" t="n">
+      <x:c r="J19" s="21" t="n">
         <x:v>0.629375</x:v>
       </x:c>
-      <x:c r="J19" s="21" t="n">
+      <x:c r="K19" s="21" t="n">
         <x:v>0.654525462962963</x:v>
       </x:c>
-      <x:c r="K19"/>
       <x:c r="L19"/>
       <x:c r="M19"/>
       <x:c r="N19"/>
@@ -1484,30 +1525,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
+        <x:v>DEMO-AION-SHA0120-01</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
         <x:v>王若曦</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="E20" s="15" t="str">
         <x:v>孙女士</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="F20" s="15" t="str">
         <x:v>158****2754</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str">
+      <x:c r="G20" s="15" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="str">
+      <x:c r="H20" s="15" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H20" s="18" t="d">
+      <x:c r="I20" s="18" t="d">
         <x:v>2026-10-09T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I20" s="21" t="n">
+      <x:c r="J20" s="21" t="n">
         <x:v>0.6750462962962963</x:v>
       </x:c>
-      <x:c r="J20" s="21" t="n">
+      <x:c r="K20" s="21" t="n">
         <x:v>0.6940740740740741</x:v>
       </x:c>
-      <x:c r="K20"/>
       <x:c r="L20"/>
       <x:c r="M20"/>
       <x:c r="N20"/>
@@ -1532,30 +1575,32 @@
         <x:v>上海吉鸿</x:v>
       </x:c>
       <x:c r="C21" s="16" t="str">
+        <x:v>DEMO-AION-SHA0120-02</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="str">
         <x:v>李若曦</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="str">
+      <x:c r="E21" s="16" t="str">
         <x:v>林先生</x:v>
       </x:c>
-      <x:c r="E21" s="16" t="str">
+      <x:c r="F21" s="16" t="str">
         <x:v>133****6187</x:v>
       </x:c>
-      <x:c r="F21" s="16" t="str">
+      <x:c r="G21" s="16" t="str">
         <x:v>销售接待</x:v>
       </x:c>
-      <x:c r="G21" s="16" t="str">
+      <x:c r="H21" s="16" t="str">
         <x:v>埃安Y Plus</x:v>
       </x:c>
-      <x:c r="H21" s="19" t="d">
+      <x:c r="I21" s="19" t="d">
         <x:v>2026-10-08T04:00:00.000Z</x:v>
       </x:c>
-      <x:c r="I21" s="22" t="n">
+      <x:c r="J21" s="22" t="n">
         <x:v>0.7119907407407408</x:v>
       </x:c>
-      <x:c r="J21" s="22" t="n">
+      <x:c r="K21" s="22" t="n">
         <x:v>0.7268981481481481</x:v>
       </x:c>
-      <x:c r="K21"/>
       <x:c r="L21"/>
       <x:c r="M21"/>
       <x:c r="N21"/>
@@ -1611,7 +1656,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="55" t="str">
-        <x:v>顾问姓名</x:v>
+        <x:v>顾问 ID</x:v>
       </x:c>
       <x:c r="B4" s="56" t="str">
         <x:v>必填</x:v>
@@ -1619,7 +1664,7 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="55" t="str">
-        <x:v>客户名称</x:v>
+        <x:v>顾问姓名</x:v>
       </x:c>
       <x:c r="B5" s="56" t="str">
         <x:v>必填</x:v>
@@ -1627,7 +1672,7 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="55" t="str">
-        <x:v>客户号码</x:v>
+        <x:v>客户名称</x:v>
       </x:c>
       <x:c r="B6" s="56" t="str">
         <x:v>必填</x:v>
@@ -1635,7 +1680,7 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="55" t="str">
-        <x:v>业务场景</x:v>
+        <x:v>客户号码</x:v>
       </x:c>
       <x:c r="B7" s="56" t="str">
         <x:v>必填</x:v>
@@ -1643,7 +1688,7 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="55" t="str">
-        <x:v>意向车系</x:v>
+        <x:v>业务场景</x:v>
       </x:c>
       <x:c r="B8" s="56" t="str">
         <x:v>必填</x:v>
@@ -1651,7 +1696,7 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="55" t="str">
-        <x:v>到访日期</x:v>
+        <x:v>意向车系</x:v>
       </x:c>
       <x:c r="B9" s="56" t="str">
         <x:v>必填</x:v>
@@ -1659,7 +1704,7 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="55" t="str">
-        <x:v>开始时间</x:v>
+        <x:v>到访日期</x:v>
       </x:c>
       <x:c r="B10" s="56" t="str">
         <x:v>必填</x:v>
@@ -1667,55 +1712,59 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="55" t="str">
-        <x:v>结束时间</x:v>
+        <x:v>开始时间</x:v>
       </x:c>
       <x:c r="B11" s="56" t="str">
         <x:v>必填</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="58" t="str">
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="55" t="str">
+        <x:v>结束时间</x:v>
+      </x:c>
+      <x:c r="B12" s="56" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="12" t="str">
         <x:v>自动补全</x:v>
       </x:c>
-      <x:c r="B12" s="59" t="str">
+      <x:c r="B13" s="60" t="str">
         <x:v>按门店编码补全品牌、大区、战区、省份、城市、巡回员及治理员。</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="58" t="str">
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="12" t="str">
         <x:v>门店匹配</x:v>
       </x:c>
-      <x:c r="B13" s="59" t="str">
+      <x:c r="B14" s="60" t="str">
         <x:v>门店编码与所属门店必须一致；无法唯一确定门店时，该行报错。</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="58" t="str">
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="12" t="str">
         <x:v>编号和号码</x:v>
       </x:c>
-      <x:c r="B14" s="58" t="str">
-        <x:v>以文本格式填写，保留前导 0。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="58" t="str">
+      <x:c r="B15" s="12" t="str">
+        <x:v>门店编码、顾问 ID 和客户号码以文本格式填写，保留前导 0。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="12" t="str">
         <x:v>日期格式</x:v>
       </x:c>
-      <x:c r="B15" s="58" t="str">
+      <x:c r="B16" s="12" t="str">
         <x:v>yyyy-mm-dd</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="58" t="str">
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="12" t="str">
         <x:v>时间格式</x:v>
       </x:c>
-      <x:c r="B16" s="58" t="str">
+      <x:c r="B17" s="12" t="str">
         <x:v>hh:mm:ss</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18"/>
